--- a/jogos_2025-05-08.xlsx
+++ b/jogos_2025-05-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="T3" t="n">
         <v>3</v>
@@ -828,53 +828,53 @@
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['14', '89']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['50', '67']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45785.51041666666</v>
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['14', '89']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45785.51041666666</v>
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>9.1</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.51</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Y8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['50', '67']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45785.51041666666</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45785.54166666666</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.72</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['69', '72', '79']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['37', '78', '82']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.2</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45785.54166666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['69', '72', '79']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '78', '82']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45785.54166666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>2.57</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>3.13</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.05</v>
+        <v>4.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['3', '31']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>['42']</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45785.54166666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T16" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
         <v>1.19</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
         <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.3</v>
+        <v>5.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['3', '31']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
         <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45785.54166666666</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Riadi Salmi</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.73</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="N20" t="n">
-        <v>1.49</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>3.06</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="T20" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['5', '59', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['29', '79']</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.68</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="O21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
         <v>1.67</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['45+5', '71']</t>
+          <t>['13', '89']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['16', '79']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['6', '46']</t>
+          <t>['15', '45+5', '73']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '75']</t>
         </is>
       </c>
       <c r="AG22" t="n">
         <v>1.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Riadi Salmi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['15', '45+5', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['39', '75']</t>
+          <t>['29', '79']</t>
         </is>
       </c>
       <c r="AG24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.08</v>
       </c>
-      <c r="AH24" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.53</v>
+        <v>3.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3610,16 +3610,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3636,65 +3636,65 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>1.54</v>
       </c>
       <c r="M25" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="X25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['5', '59', '90+4']</t>
+          <t>['6', '46']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="T26" t="n">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
         <v>1.67</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['13', '89']</t>
+          <t>['45+5', '71']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['16', '79']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.55</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45785.66666666666</v>
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
         <v>1.15</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI27" t="n">
         <v>1.5</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W28" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG28" t="n">
         <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" t="n">
         <v>1.5</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.59</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="O30" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
         <v>1.44</v>
@@ -4317,10 +4317,10 @@
         <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
         <v>1.61</v>
@@ -4332,32 +4332,32 @@
         <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['39', '55', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['15', '49']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['7', '26', '48']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45785.89583333334</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.2</v>
+        <v>3.59</v>
       </c>
       <c r="M31" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="N31" t="n">
-        <v>2.86</v>
+        <v>1.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
         <v>1.44</v>
@@ -4446,10 +4446,10 @@
         <v>1.4</v>
       </c>
       <c r="X31" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
         <v>1.61</v>
@@ -4461,32 +4461,32 @@
         <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['39', '55', '90+3']</t>
+          <t>['15', '49']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['7', '26', '48']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45785.89583333334</v>
